--- a/teaching_jobs_china_20260514.xlsx
+++ b/teaching_jobs_china_20260514.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teaching Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Teaching Jobs'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Teaching Jobs'!$A$1:$J$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002E5A88"/>
         <bgColor rgb="002E5A88"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0F7"/>
+        <bgColor rgb="00E8F0F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,11 +71,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,8 +516,584 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Zhejiang Wenhe Talent Development Co., LTD</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International School English Teacher </t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Hangzhou</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>≤25000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108737</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>According to the company's strategic plan - develop after-school business and improve the quality and influence of foreign teachers' oral English class. The company has adjusted its organizational str...</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Gushang Technology (Wuhan) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Middle&amp;High School IBDP English Teacher</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>25000 - 35000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108889</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Job Details:
+-Work Load: around 20 classes/week(45mins/class)+office hrs M-F+weekends off
+-Type of school: int’l school
+-Students age:14-18
+-Contract period:2-year
+-Location:Changshu city under Suzhou...</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Work visa, Air travel allowance, Medical &amp; accidental insurance, Free apartment, paid holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Gushang Technology (Wuhan) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>High School English Teacher</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chengdu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>25000 - 35000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355107031</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Job Details:
+-Work Load:Up to 24 classes/week(40mins/class)+office hrs+weekends off
+-Type of school: private school
+-Curriculum:Canadian curriculum
+-Location:Pidu dist.,Chengdu
+-Vacancy: 1 High School...</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Work visa, Air travel allowance, Medical &amp; accidental insurance, Free apartment, paid holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Xudashan Consulting Co.ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Cambridge High School English Teacher</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>25000 - 35000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108881</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Cambridge English Teacher (Senior High School) Wanted for an International School in Beijing
+Location: Beijing
+Start Date: August 2026
+We are seeking an experienced and dedicated Cambridge English tea...</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>X-GIANTS  (Shanghai) Human Resources Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>IBDP EAL Teacher（English B）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>30000 - 40000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355106923</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Job Description: IB DP EAL Teacher
+#Consider outstanding candidates for the HOD position.
+School: IB World School – Suzhou
+Established: Approx. 10 years
+Type: IB Certified K–12 School
+Students: Approx...</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Shanghai Enrich Education Technology Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Foreign English Teacher</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>20000 - 25000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Full Time|Part Time</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108413</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>❇️Responsibilities:
+1. Teaching 
+2. Supporting demo class or marketing activities if any;
+3. Curriculum developing if any;
+5. Student oral test;
+6. Other responsibilities according to the company’s re...</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Work visa, Paid annual leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Beijing Yingcai Dingsheng Education Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>English Teacher</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>25000 - 30000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355106587</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Beijing reading club need native foreigner teacher
+Work date: June 2026
+Location: Chaoyang district shuangjing station
+1. QUALIFICATIONS
+2. 1. Native English speaker,male only
+3. 2. B.A. or M.A. in E...</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>London Teacher Training College,China TEFL Branch</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Middle School Economics Teacher</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>20000 - 25000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108811</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Responsibility:to teach Economics (MYP) +Oral English in Junior High
+Office Working Hours :Monday-Friday 07:45-12:15 and 14:30-17:50
+Students age: 12-15 years old,
+Location:Guangzhou
+Salary:20k+free ...</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Paid annual leave, Air travel allowance, Medical &amp; accidental insurance, Free meal, Free apartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TiC, ticket into China</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>AP Humanities Teacher</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chengdu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>25000 - 32000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108885</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSIBILITY
+1. Design and implement rigorous, engaging AP Humanities curricula covering all core themes.
+2. Use diverse teaching and assessment methods to meet students’ learning needs and foster c...</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Work visa, Paid annual leave, Air travel allowance, Transportation allowance, Medical &amp; accidental insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Zhangjiagang Shine Compass Kindergarten</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Native English Teacher Wanted for Kinder</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>16000 - 22000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355104953</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Responsibilities
+  1.Plan and deliver age‑appropriate English lessons with games, songs and interactive activities.
+  2.Build a positive, supportive classroom environment for children’s learning and g...</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Work visa, Paid annual leave, Air travel allowance, Medical &amp; accidental insurance, Free meal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>To Summer Information Consulting Co., Ltd</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle School English Teacher </t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>17000 - 18000 CNY /Month</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.echinacities.com/jobs/detail?id=1355108093</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Job Title: Middle School English Teacher 
+Location: Shenzhen
+School type: Public School
+Position Type: Full time
+Starting Date: ASAP 
+Working time: Monday to Friday 
+Monthly salary package: 17k-18k be...</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Work visa, Paid annual leave, Air travel allowance, Medical &amp; accidental insurance, contract completion bonus</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>